--- a/data/processed/harmonization/Isotopes__Soil_organic_carbon_delta13C/10.15485_2283432/10.15485_2283432_soil_Isotopes__Soil_organic_carbon_delta13C.xlsx
+++ b/data/processed/harmonization/Isotopes__Soil_organic_carbon_delta13C/10.15485_2283432/10.15485_2283432_soil_Isotopes__Soil_organic_carbon_delta13C.xlsx
@@ -431,8 +431,8 @@
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
@@ -518,12 +518,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>187946</t>
+          <t>0-20:187946</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -570,12 +570,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>187947</t>
+          <t>20-40:187947</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -622,12 +622,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>187948</t>
+          <t>40-60:187948</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>187949</t>
+          <t>60-100:187949</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -726,12 +726,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>187950</t>
+          <t>0-20:187950</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>188051</t>
+          <t>20-40:188051</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -830,12 +830,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>187951</t>
+          <t>40-60:187951</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -882,12 +882,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>187952</t>
+          <t>60-100:187952</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -934,12 +934,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>187955</t>
+          <t>0-20:187955</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>187956</t>
+          <t>20-40:187956</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>187957</t>
+          <t>40-60:187957</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>188054</t>
+          <t>60-100:188054</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>187953</t>
+          <t>0-20:187953</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>187954</t>
+          <t>20-40:187954</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1246,12 +1246,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>188052</t>
+          <t>40-60:188052</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1298,12 +1298,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>188053</t>
+          <t>60-100:188053</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>187946</t>
+          <t>0-20:187946</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>187947</t>
+          <t>20-40:187947</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>187948</t>
+          <t>40-60:187948</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1506,12 +1506,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>187949</t>
+          <t>60-100:187949</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1558,12 +1558,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>187950</t>
+          <t>0-20:187950</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>187951</t>
+          <t>40-60:187951</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1662,12 +1662,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>187952</t>
+          <t>60-100:187952</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>187955</t>
+          <t>0-20:187955</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>187956</t>
+          <t>20-40:187956</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1818,12 +1818,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>187957</t>
+          <t>40-60:187957</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1870,12 +1870,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>188054</t>
+          <t>60-100:188054</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>187953</t>
+          <t>0-20:187953</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1974,12 +1974,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>187954</t>
+          <t>20-40:187954</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2026,12 +2026,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>188052</t>
+          <t>40-60:188052</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2078,12 +2078,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>188053</t>
+          <t>60-100:188053</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Radiocarbon Laboratory Sample Number</t>
+          <t>depth:Radiocarbon Laboratory Sample Number</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
